--- a/processed_ruby_restored_xlsx/sc112_ノノ２：恋人化.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc112_ノノ２：恋人化.ss.xlsx
@@ -545,8 +545,8 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>I watched from the edge of the classroom as Rin-chan's
-call signaled the end-of-class greetings.</t>
+          <t>I watched from the edge of the classroom as
+Rin-chan's call signaled the end-of-class greetings.</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -561,8 +561,9 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Lately it's been my routine to help Nono-chan, so it's
-not an exaggeration to say I'm always up during class.</t>
+          <t>Lately it's been my routine to help Nono-chan, so
+it's not an exaggeration to say I'm always up during
+class.</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -669,8 +670,8 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>Judging by how flustered she was, I figure she must've
-been holding it in since class.</t>
+          <t>Judging by how flustered she was, I figure she
+must've been holding it in since class.</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -961,8 +962,8 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>I stood at attention behind Nono-chan and watched over
-her as if I were her guardian.</t>
+          <t>I stood at attention behind Nono-chan and watched
+over her as if I were her guardian.</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1070,8 +1071,8 @@
       <c r="B40" s="1" t="inlineStr">
         <is>
           <t>「Well... it's my first summer vacation in Japan, so I
-want to do something that will stay with me for a long
-time！」</t>
+want to do something that will stay with me for a
+long time！」</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1132,8 +1133,8 @@
       <c r="B44" s="1" t="inlineStr">
         <is>
           <t>「When you put it that way, yeah... it's just that I
-still don't know what I should do, so I think anything
-will be fun！」</t>
+still don't know what I should do, so I think
+anything will be fun！」</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1178,8 +1179,8 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>Watching Nono-chan talk with that cheerful look on her
-face, I want to give her some happy memories.</t>
+          <t>Watching Nono-chan talk with that cheerful look on
+her face, I want to give her some happy memories.</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1210,8 +1211,8 @@
       <c r="B49" s="1" t="inlineStr">
         <is>
           <t>「When you think of summer vacation in Japan, there's
-fireworks festivals, matsuri, pools... well, all sorts
-of things, right？」</t>
+fireworks festivals, matsuri, pools... well, all
+sorts of things, right？」</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1271,7 +1272,8 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>「Ooh...！ I definitely want to see Japanese fireworks！」</t>
+          <t>「Ooh...！ I definitely want to see Japanese
+fireworks！」</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1301,8 +1303,9 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>「I've seen fireworks in the States too, but I've heard
-Japanese fireworks are in a whole different league！」</t>
+          <t>「I've seen fireworks in the States too, but I've
+heard Japanese fireworks are in a whole different
+league！」</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1392,8 +1395,8 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>「Is that so？ Fireworks must look beautiful in the cold
-season, right？」</t>
+          <t>「Is that so？ Fireworks must look beautiful in the
+cold season, right？」</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -2234,8 +2237,8 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>「About the next homeroom activity—what do you think we
-should do？」</t>
+          <t>「About the next homeroom activity—what do you think
+we should do？」</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2586,9 +2589,9 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan, sticking strictly to her role as a teacher,
-pouted her lips over the secrecy of the lesson
-content.</t>
+          <t>Nono-chan, sticking strictly to her role as a
+teacher, pouted her lips over the secrecy of the
+lesson content.</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -3232,8 +3235,8 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>Tomorrow, I'm definitely going to give a class they'll
-remember！！</t>
+          <t>Tomorrow, I'm definitely going to give a class
+they'll remember！！</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3278,7 +3281,8 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>「...So, you really didn't make the handout after all？」</t>
+          <t>「...So, you really didn't make the handout after
+all？」</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3308,7 +3312,8 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha... sorry, work's been busy and I kinda just...」</t>
+          <t>「Ahaha... sorry, work's been busy and I kinda
+just...」</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3741,8 +3746,8 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>Both Miru-chan and Rin-chan jumped on Rurichiyo-chan's
-words.</t>
+          <t>Both Miru-chan and Rin-chan jumped on
+Rurichiyo-chan's words.</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3757,7 +3762,8 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>This is turning out to be really convenient for me...！</t>
+          <t>This is turning out to be really convenient for
+me...！</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3957,8 +3963,8 @@
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t>When Miru-chan answered cheerfully, Rurichiyo-chan and
-Rin-chan followed suit and moved.</t>
+          <t>When Miru-chan answered cheerfully, Rurichiyo-chan
+and Rin-chan followed suit and moved.</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -4432,8 +4438,8 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>It didn't seem like she was just going along with it —
-she might actually be into the idea.</t>
+          <t>It didn't seem like she was just going along with it
+— she might actually be into the idea.</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4631,9 +4637,9 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>She already knows everything, so being in the position
-of being taught probably leaves her with nothing to
-do.</t>
+          <t>She already knows everything, so being in the
+position of being taught probably leaves her with
+nothing to do.</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -5093,7 +5099,8 @@
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t>They return to the lesson without pressing the matter.</t>
+          <t>They return to the lesson without pressing the
+matter.</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5108,8 +5115,8 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>Then Miru-chan starts folding a small note and sending
-it toward Rin-chan.</t>
+          <t>Then Miru-chan starts folding a small note and
+sending it toward Rin-chan.</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5154,8 +5161,8 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan reads Miru-chan's note and nods to herself as
-if satisfied.</t>
+          <t>Rin-chan reads Miru-chan's note and nods to herself
+as if satisfied.</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5595,8 +5602,8 @@
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t>I stopped what I was doing and watched the interaction
-between the girls.</t>
+          <t>I stopped what I was doing and watched the
+interaction between the girls.</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -5859,8 +5866,8 @@
       <c r="B352" s="1" t="inlineStr">
         <is>
           <t>You were fidgeting because you had too much time on
-your hands, and they probably mistook that for wanting
-to go to the restroom.</t>
+your hands, and they probably mistook that for
+wanting to go to the restroom.</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -6029,8 +6036,8 @@
       </c>
       <c r="B363" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan and Rin-chan seem like they're butting heads
-even without talking.</t>
+          <t>Miru-chan and Rin-chan seem like they're butting
+heads even without talking.</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -6152,8 +6159,8 @@
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t>Thinking that, I pretended nothing had happened, and I
-sensed Nono-chan moving.</t>
+          <t>Thinking that, I pretended nothing had happened, and
+I sensed Nono-chan moving.</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -6318,8 +6325,8 @@
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan stood up, gave a small bow, then hurried out
-of the classroom.</t>
+          <t>Nono-chan stood up, gave a small bow, then hurried
+out of the classroom.</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -6334,8 +6341,8 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t>...She was just covering it up; she really did need to
-go to the bathroom.</t>
+          <t>...She was just covering it up; she really did need
+to go to the bathroom.</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -6687,8 +6694,8 @@
       <c r="B406" s="1" t="inlineStr">
         <is>
           <t>She’s desperately trying to stifle her voice, but
-ending up shaking her shoulders — whatever was written
-must have been really funny.</t>
+ending up shaking her shoulders — whatever was
+written must have been really funny.</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -6839,8 +6846,9 @@
       </c>
       <c r="B416" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan tries to play it off nonchalantly, but she's
-holding the origami crane carefully in her hands.</t>
+          <t>Nono-chan tries to play it off nonchalantly, but
+she's holding the origami crane carefully in her
+hands.</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -6855,8 +6863,8 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t>I see — Rurichiyo-chan folded it and showed it to her,
-and that got her all worked up.</t>
+          <t>I see — Rurichiyo-chan folded it and showed it to
+her, and that got her all worked up.</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -6871,8 +6879,8 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>So she even forgot to hide it and is holding it in her
-hand... right.</t>
+          <t>So she even forgot to hide it and is holding it in
+her hand... right.</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -7056,8 +7064,8 @@
       <c r="B430" s="1" t="inlineStr">
         <is>
           <t>Feeling all warm and cozy, I—forgetting the
-teacher-student boundary—read the words written on the
-belly of the origami crane.</t>
+teacher-student boundary—read the words written on
+the belly of the origami crane.</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -7226,8 +7234,8 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>Unable to contain my curiosity, I took advantage of my
-position as a teacher and said it to Nono.</t>
+          <t>Unable to contain my curiosity, I took advantage of
+my position as a teacher and said it to Nono.</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -8281,8 +8289,8 @@
       </c>
       <c r="B510" s="1" t="inlineStr">
         <is>
-          <t>When I picked her in a flustered attempt to save face,
-Rin-chan made a 'darn！' sort of face.</t>
+          <t>When I picked her in a flustered attempt to save
+face, Rin-chan made a 'darn！' sort of face.</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -8525,7 +8533,8 @@
       </c>
       <c r="B526" s="1" t="inlineStr">
         <is>
-          <t>「Eh...? I-I do know！ It's a kind of security, right！?」</t>
+          <t>「Eh...? I-I do know！ It's a kind of security,
+right！?」</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -8739,9 +8748,9 @@
       </c>
       <c r="B540" s="1" t="inlineStr">
         <is>
-          <t>Also, I chose it because everyone could do it together
-and it would leave a lasting shape, but maybe she
-really didn't know about it.</t>
+          <t>Also, I chose it because everyone could do it
+together and it would leave a lasting shape, but
+maybe she really didn't know about it.</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -9047,9 +9056,9 @@
       </c>
       <c r="B560" s="1" t="inlineStr">
         <is>
-          <t>However, since we'd use more paint than in regular art
-class, we decided to bring our individual paint kits
-together.</t>
+          <t>However, since we'd use more paint than in regular
+art class, we decided to bring our individual paint
+kits together.</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -9126,8 +9135,8 @@
       </c>
       <c r="B565" s="1" t="inlineStr">
         <is>
-          <t>「Okaaay！ Rin, I'll put it on for you, so—hold out your
-hand~」</t>
+          <t>「Okaaay！ Rin, I'll put it on for you, so—hold out
+your hand~」</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -9371,8 +9380,8 @@
       </c>
       <c r="B581" s="1" t="inlineStr">
         <is>
-          <t>Watching in silence, it ended up that Rin-chan started
-painting Rurichiyo-chan with the paints.</t>
+          <t>Watching in silence, it ended up that Rin-chan
+started painting Rurichiyo-chan with the paints.</t>
         </is>
       </c>
       <c r="C581" t="n">
@@ -9447,9 +9456,9 @@
       </c>
       <c r="B586" s="1" t="inlineStr">
         <is>
-          <t>So it really is ticklish — Rurichiyo-chan bit back the
-feeling in her palms and couldn't help but let out a
-small sigh.</t>
+          <t>So it really is ticklish — Rurichiyo-chan bit back
+the feeling in her palms and couldn't help but let
+out a small sigh.</t>
         </is>
       </c>
       <c r="C586" t="n">
@@ -9678,8 +9687,8 @@
       </c>
       <c r="B601" s="1" t="inlineStr">
         <is>
-          <t>Even though Rin-chan immediately teases her, Nono-chan
-can't protest and only stiffens her body.</t>
+          <t>Even though Rin-chan immediately teases her,
+Nono-chan can't protest and only stiffens her body.</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -10045,8 +10054,8 @@
       <c r="B625" s="1" t="inlineStr">
         <is>
           <t>Maybe she's taking revenge for being teased earlier;
-Nono-chan, unusually mean-faced, runs her brush across
-the paper.</t>
+Nono-chan, unusually mean-faced, runs her brush
+across the paper.</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -10621,8 +10630,8 @@
       </c>
       <c r="B663" s="1" t="inlineStr">
         <is>
-          <t>The bristles of the paintbrush rubbing against it feel
-indescribable.</t>
+          <t>The bristles of the paintbrush rubbing against it
+feel indescribable.</t>
         </is>
       </c>
       <c r="C663" t="n">
@@ -10698,7 +10707,8 @@
       </c>
       <c r="B668" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan said that and added more paint to her brush.</t>
+          <t>Nono-chan said that and added more paint to her
+brush.</t>
         </is>
       </c>
       <c r="C668" t="n">
@@ -11211,8 +11221,8 @@
       </c>
       <c r="B702" s="1" t="inlineStr">
         <is>
-          <t>But seeing Rin-chan and Rurichiyo-chan teasing her and
-watching her get embarrassed made me feel all
+          <t>But seeing Rin-chan and Rurichiyo-chan teasing her
+and watching her get embarrassed made me feel all
 fluttery.</t>
         </is>
       </c>
@@ -11580,8 +11590,8 @@
       </c>
       <c r="B726" s="1" t="inlineStr">
         <is>
-          <t>Everyone smiles happily when they look at the finished
-handprint.</t>
+          <t>Everyone smiles happily when they look at the
+finished handprint.</t>
         </is>
       </c>
       <c r="C726" t="n">
@@ -11765,8 +11775,8 @@
       <c r="B738" s="1" t="inlineStr">
         <is>
           <t>For some reason, Nono-chan has started getting
-excited, and she’s directing her sparkling eyes at the
-piece she just made.</t>
+excited, and she’s directing her sparkling eyes at
+the piece she just made.</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -12105,8 +12115,8 @@
       </c>
       <c r="B760" s="1" t="inlineStr">
         <is>
-          <t>The whole sheet of pure white drawing paper was, in no
-time, filled with tiny handprints.</t>
+          <t>The whole sheet of pure white drawing paper was, in
+no time, filled with tiny handprints.</t>
         </is>
       </c>
       <c r="C760" t="n">
@@ -12634,8 +12644,8 @@
       <c r="B794" s="1" t="inlineStr">
         <is>
           <t>I thought ‘great hardship’ wasn’t something you’d say
-to these kids, but homework… well, that might actually
-be true.</t>
+to these kids, but homework… well, that might
+actually be true.</t>
         </is>
       </c>
       <c r="C794" t="n">
@@ -13058,8 +13068,8 @@
       </c>
       <c r="B821" s="1" t="inlineStr">
         <is>
-          <t>「Every place we went together was fun because you were
-there, and they all became memories I cherish.」</t>
+          <t>「Every place we went together was fun because you
+were there, and they all became memories I cherish.」</t>
         </is>
       </c>
       <c r="C821" t="n">
@@ -13793,8 +13803,8 @@
       <c r="B869" s="1" t="inlineStr">
         <is>
           <t>Thinking that, I can even understand why Miru-chan
-muttered with that face like she’d bitten on something
-bitter.</t>
+muttered with that face like she’d bitten on
+something bitter.</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -13824,8 +13834,8 @@
       </c>
       <c r="B871" s="1" t="inlineStr">
         <is>
-          <t>「If it's a 'tokken', I think you could also choose not
-to hand it out.」</t>
+          <t>「If it's a 'tokken', I think you could also choose
+not to hand it out.」</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -14131,8 +14141,8 @@
       </c>
       <c r="B891" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan also receives the report card with both
-hands.</t>
+          <t>Rurichiyo-chan also receives the report card with
+both hands.</t>
         </is>
       </c>
       <c r="C891" t="n">
@@ -14301,8 +14311,8 @@
       </c>
       <c r="B902" s="1" t="inlineStr">
         <is>
-          <t>Whether Nono was forgetful or was knowingly letting it
-slide, she answered naturally.</t>
+          <t>Whether Nono was forgetful or was knowingly letting
+it slide, she answered naturally.</t>
         </is>
       </c>
       <c r="C902" t="n">
@@ -14408,8 +14418,8 @@
       </c>
       <c r="B909" s="1" t="inlineStr">
         <is>
-          <t>...What I made was a report card in the same format as
-everyone else's.</t>
+          <t>...What I made was a report card in the same format
+as everyone else's.</t>
         </is>
       </c>
       <c r="C909" t="n">
@@ -14669,8 +14679,8 @@
       </c>
       <c r="B926" s="1" t="inlineStr">
         <is>
-          <t>Then she gave a small laugh and hugged the report card
-to her chest.</t>
+          <t>Then she gave a small laugh and hugged the report
+card to her chest.</t>
         </is>
       </c>
       <c r="C926" t="n">
@@ -14716,8 +14726,8 @@
       </c>
       <c r="B929" s="1" t="inlineStr">
         <is>
-          <t>「Come to think of it, Onii-chan, you're a teacher too,
-right?」</t>
+          <t>「Come to think of it, Onii-chan, you're a teacher
+too, right?」</t>
         </is>
       </c>
       <c r="C929" t="n">
@@ -14809,8 +14819,9 @@
       </c>
       <c r="B935" s="1" t="inlineStr">
         <is>
-          <t>Strictly speaking it's a teacher-student relationship,
-but before that they're just friends the same age.</t>
+          <t>Strictly speaking it's a teacher-student
+relationship, but before that they're just friends
+the same age.</t>
         </is>
       </c>
       <c r="C935" t="n">
@@ -14901,8 +14912,8 @@
       </c>
       <c r="B941" s="1" t="inlineStr">
         <is>
-          <t>At the closing ceremony I kept wondering why she came,
-but thinking it over, isn't this a chance to
+          <t>At the closing ceremony I kept wondering why she
+came, but thinking it over, isn't this a chance to
 negotiate?！</t>
         </is>
       </c>
@@ -15041,8 +15052,8 @@
       </c>
       <c r="B950" s="1" t="inlineStr">
         <is>
-          <t>When I got close enough that I didn't need to shout, I
-took a secret deep breath and called out.</t>
+          <t>When I got close enough that I didn't need to shout,
+I took a secret deep breath and called out.</t>
         </is>
       </c>
       <c r="C950" t="n">
@@ -15457,8 +15468,8 @@
       </c>
       <c r="B977" s="1" t="inlineStr">
         <is>
-          <t>She slips back into her usual tone, which makes things
-awkward.</t>
+          <t>She slips back into her usual tone, which makes
+things awkward.</t>
         </is>
       </c>
       <c r="C977" t="n">
@@ -15548,8 +15559,8 @@
       </c>
       <c r="B983" s="1" t="inlineStr">
         <is>
-          <t>「I want you to make it so she can stay at this academy
-even after summer break is over！」</t>
+          <t>「I want you to make it so she can stay at this
+academy even after summer break is over！」</t>
         </is>
       </c>
       <c r="C983" t="n">
@@ -15609,8 +15620,8 @@
       </c>
       <c r="B987" s="1" t="inlineStr">
         <is>
-          <t>But her face was a complete poker face, giving away no
-emotion at all.</t>
+          <t>But her face was a complete poker face, giving away
+no emotion at all.</t>
         </is>
       </c>
       <c r="C987" t="n">
@@ -15900,7 +15911,8 @@
       </c>
       <c r="B1006" s="1" t="inlineStr">
         <is>
-          <t>「Well… she'll keep being everyone's homeroom teacher…」</t>
+          <t>「Well… she'll keep being everyone's homeroom
+teacher…」</t>
         </is>
       </c>
       <c r="C1006" t="n">
@@ -16253,8 +16265,8 @@
       </c>
       <c r="B1029" s="1" t="inlineStr">
         <is>
-          <t>「Haaah... You don't really think such selfishness will
-fly, do you？」</t>
+          <t>「Haaah... You don't really think such selfishness
+will fly, do you？」</t>
         </is>
       </c>
       <c r="C1029" t="n">
@@ -16497,8 +16509,8 @@
       </c>
       <c r="B1045" s="1" t="inlineStr">
         <is>
-          <t>Knowing that, she's probably stalling on a decision to
-keep her options open.</t>
+          <t>Knowing that, she's probably stalling on a decision
+to keep her options open.</t>
         </is>
       </c>
       <c r="C1045" t="n">
@@ -16623,7 +16635,8 @@
       </c>
       <c r="B1053" s="1" t="inlineStr">
         <is>
-          <t>But, I don't know, it just doesn't suit me after all….</t>
+          <t>But, I don't know, it just doesn't suit me after
+all….</t>
         </is>
       </c>
       <c r="C1053" t="n">
@@ -17245,7 +17258,8 @@
       </c>
       <c r="B1094" s="1" t="inlineStr">
         <is>
-          <t>I could tell she was happy, but that's a bit dramatic.</t>
+          <t>I could tell she was happy, but that's a bit
+dramatic.</t>
         </is>
       </c>
       <c r="C1094" t="n">
@@ -17502,8 +17516,8 @@
       </c>
       <c r="B1111" s="1" t="inlineStr">
         <is>
-          <t>I took a few seconds to calm myself, gave a short nod,
-and waited for Nono-chan to continue.</t>
+          <t>I took a few seconds to calm myself, gave a short
+nod, and waited for Nono-chan to continue.</t>
         </is>
       </c>
       <c r="C1111" t="n">
@@ -17533,8 +17547,8 @@
       </c>
       <c r="B1113" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei always cared about me... your messages
-meant so much to me.」</t>
+          <t>「Janitor-sensei always cared about me... your
+messages meant so much to me.」</t>
         </is>
       </c>
       <c r="C1113" t="n">
@@ -17611,7 +17625,8 @@
       </c>
       <c r="B1118" s="1" t="inlineStr">
         <is>
-          <t>...Nono-chan suddenly starts stringing words together.</t>
+          <t>...Nono-chan suddenly starts stringing words
+together.</t>
         </is>
       </c>
       <c r="C1118" t="n">
@@ -18333,7 +18348,8 @@
       <c r="B1165" s="1" t="inlineStr">
         <is>
           <t>At first she was hedging with words like 'maybe', but
-when she said it properly again she said it for sure…！</t>
+when she said it properly again she said it for
+sure…！</t>
         </is>
       </c>
       <c r="C1165" t="n">
@@ -18380,8 +18396,8 @@
         <is>
           <t>Nono-chan seemed to get embarrassed halfway through
 rephrasing it and blurted out something like, "What
-should I do？", and even now her face is bright red and
-she's trembling.</t>
+should I do？", and even now her face is bright red
+and she's trembling.</t>
         </is>
       </c>
       <c r="C1168" t="n">
@@ -19278,8 +19294,8 @@
       </c>
       <c r="B1227" s="1" t="inlineStr">
         <is>
-          <t>「And... thank you for saying you like me... I like you
-too, Nono-chan.」</t>
+          <t>「And... thank you for saying you like me... I like
+you too, Nono-chan.」</t>
         </is>
       </c>
       <c r="C1227" t="n">
@@ -19475,7 +19491,8 @@
       <c r="B1240" s="1" t="inlineStr">
         <is>
           <t>After feeling somehow relieved and getting back to
-herself, Nono-chan blushed again and dropped her tone.</t>
+herself, Nono-chan blushed again and dropped her
+tone.</t>
         </is>
       </c>
       <c r="C1240" t="n">
@@ -19595,8 +19612,8 @@
       </c>
       <c r="B1248" s="1" t="inlineStr">
         <is>
-          <t>「But is it okay with you, Janitor-sensei, that someone
-as tiny as me is your girlfriend？」</t>
+          <t>「But is it okay with you, Janitor-sensei, that
+someone as tiny as me is your girlfriend？」</t>
         </is>
       </c>
       <c r="C1248" t="n">
@@ -19779,8 +19796,8 @@
       </c>
       <c r="B1260" s="1" t="inlineStr">
         <is>
-          <t>Maybe she felt a little better thinking she was in the
-same position as me, who’s older.</t>
+          <t>Maybe she felt a little better thinking she was in
+the same position as me, who’s older.</t>
         </is>
       </c>
       <c r="C1260" t="n">
@@ -20128,7 +20145,8 @@
       </c>
       <c r="B1283" s="1" t="inlineStr">
         <is>
-          <t>We drew our faces close and pressed our lips together.</t>
+          <t>We drew our faces close and pressed our lips
+together.</t>
         </is>
       </c>
       <c r="C1283" t="n">
@@ -20203,8 +20221,8 @@
       </c>
       <c r="B1288" s="1" t="inlineStr">
         <is>
-          <t>First we lightly brushed our lips together, exchanging
-gentle, pecking kisses.</t>
+          <t>First we lightly brushed our lips together,
+exchanging gentle, pecking kisses.</t>
         </is>
       </c>
       <c r="C1288" t="n">
@@ -20665,8 +20683,8 @@
       </c>
       <c r="B1318" s="1" t="inlineStr">
         <is>
-          <t>This time, it was the other way around again—Nono-chan
-licked my lips with her tongue.</t>
+          <t>This time, it was the other way around
+again—Nono-chan licked my lips with her tongue.</t>
         </is>
       </c>
       <c r="C1318" t="n">
@@ -20923,8 +20941,8 @@
       </c>
       <c r="B1335" s="1" t="inlineStr">
         <is>
-          <t>When I pulled my face away, Nono-chan called out to me
-in a hesitant voice.</t>
+          <t>When I pulled my face away, Nono-chan called out to
+me in a hesitant voice.</t>
         </is>
       </c>
       <c r="C1335" t="n">
@@ -20939,8 +20957,8 @@
       </c>
       <c r="B1336" s="1" t="inlineStr">
         <is>
-          <t>Then when I looked back, I ended up seeing their eyes,
-moist and so close, and it made my heart skip.</t>
+          <t>Then when I looked back, I ended up seeing their
+eyes, moist and so close, and it made my heart skip.</t>
         </is>
       </c>
       <c r="C1336" t="n">
@@ -21064,7 +21082,8 @@
       </c>
       <c r="B1344" s="1" t="inlineStr">
         <is>
-          <t>You want me to treat you like a grown-up woman, right？</t>
+          <t>You want me to treat you like a grown-up woman,
+right？</t>
         </is>
       </c>
       <c r="C1344" t="n">
@@ -21245,8 +21264,8 @@
       </c>
       <c r="B1356" s="1" t="inlineStr">
         <is>
-          <t>Seeing Nono-chan lying on the bed in only her panties,
-I couldn't help swalling.</t>
+          <t>Seeing Nono-chan lying on the bed in only her
+panties, I couldn't help swalling.</t>
         </is>
       </c>
       <c r="C1356" t="n">
@@ -21550,8 +21569,8 @@
       </c>
       <c r="B1376" s="1" t="inlineStr">
         <is>
-          <t>Maybe she wasn't confident in her body, and that's why
-she wanted to find out？</t>
+          <t>Maybe she wasn't confident in her body, and that's
+why she wanted to find out？</t>
         </is>
       </c>
       <c r="C1376" t="n">
@@ -21673,8 +21692,8 @@
       </c>
       <c r="B1384" s="1" t="inlineStr">
         <is>
-          <t>When I cleaned up the blunt truth into nicer words and
-said it, Nono-chan went bright red and let out a
+          <t>When I cleaned up the blunt truth into nicer words
+and said it, Nono-chan went bright red and let out a
 groan.</t>
         </is>
       </c>
@@ -22044,8 +22063,8 @@
       </c>
       <c r="B1408" s="1" t="inlineStr">
         <is>
-          <t>But my palm noticed that Nono-chan's body was reacting
-sensitively to it.</t>
+          <t>But my palm noticed that Nono-chan's body was
+reacting sensitively to it.</t>
         </is>
       </c>
       <c r="C1408" t="n">
@@ -22716,8 +22735,8 @@
       </c>
       <c r="B1452" s="1" t="inlineStr">
         <is>
-          <t>I thought that and nodded, but that doesn't mean I can
-stop my hand.</t>
+          <t>I thought that and nodded, but that doesn't mean I
+can stop my hand.</t>
         </is>
       </c>
       <c r="C1452" t="n">
@@ -22868,8 +22887,8 @@
       </c>
       <c r="B1462" s="1" t="inlineStr">
         <is>
-          <t>When I cut off Nono-chan's words and asked, she pouted
-again.</t>
+          <t>When I cut off Nono-chan's words and asked, she
+pouted again.</t>
         </is>
       </c>
       <c r="C1462" t="n">
@@ -22989,9 +23008,9 @@
       </c>
       <c r="B1470" s="1" t="inlineStr">
         <is>
-          <t>Even though she's flustered and fumbling, it's lacking
-its usual force — that probably shows a complicated
-mix of feelings.</t>
+          <t>Even though she's flustered and fumbling, it's
+lacking its usual force — that probably shows a
+complicated mix of feelings.</t>
         </is>
       </c>
       <c r="C1470" t="n">
@@ -23326,8 +23345,8 @@
       </c>
       <c r="B1492" s="1" t="inlineStr">
         <is>
-          <t>「Actually, it's already gotten to the point where it's
-kind of wrong...」</t>
+          <t>「Actually, it's already gotten to the point where
+it's kind of wrong...」</t>
         </is>
       </c>
       <c r="C1492" t="n">
@@ -23342,7 +23361,8 @@
       </c>
       <c r="B1493" s="1" t="inlineStr">
         <is>
-          <t>Thinking it's a good moment, I pull down my underwear.</t>
+          <t>Thinking it's a good moment, I pull down my
+underwear.</t>
         </is>
       </c>
       <c r="C1493" t="n">
@@ -23433,8 +23453,8 @@
       </c>
       <c r="B1499" s="1" t="inlineStr">
         <is>
-          <t>「...It's because you found me cute, Nono-chan, that it
-ended up like this...」</t>
+          <t>「...It's because you found me cute, Nono-chan, that
+it ended up like this...」</t>
         </is>
       </c>
       <c r="C1499" t="n">
@@ -23495,8 +23515,8 @@
       </c>
       <c r="B1503" s="1" t="inlineStr">
         <is>
-          <t>Even if I can handle ordinary studying, I still have a
-lot to learn about sexy studying.</t>
+          <t>Even if I can handle ordinary studying, I still have
+a lot to learn about sexy studying.</t>
         </is>
       </c>
       <c r="C1503" t="n">
@@ -23587,8 +23607,8 @@
       </c>
       <c r="B1509" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... when the other person feels good, it makes me
-happy.」</t>
+          <t>「Yeah... when the other person feels good, it makes
+me happy.」</t>
         </is>
       </c>
       <c r="C1509" t="n">
@@ -23663,8 +23683,8 @@
       </c>
       <c r="B1514" s="1" t="inlineStr">
         <is>
-          <t>It was a brief exchange of words, but I understood how
-Nono-chan felt.</t>
+          <t>It was a brief exchange of words, but I understood
+how Nono-chan felt.</t>
         </is>
       </c>
       <c r="C1514" t="n">
@@ -24047,8 +24067,8 @@
       </c>
       <c r="B1539" s="1" t="inlineStr">
         <is>
-          <t>「Y-yes... the penis goes into between my legs and then
-shoots semen inside, right...?！」</t>
+          <t>「Y-yes... the penis goes into between my legs and
+then shoots semen inside, right...?！」</t>
         </is>
       </c>
       <c r="C1539" t="n">
@@ -24445,7 +24465,8 @@
       </c>
       <c r="B1565" s="1" t="inlineStr">
         <is>
-          <t>I speak while thinking so Nono-chan can understand me.</t>
+          <t>I speak while thinking so Nono-chan can understand
+me.</t>
         </is>
       </c>
       <c r="C1565" t="n">
@@ -24583,8 +24604,8 @@
       </c>
       <c r="B1574" s="1" t="inlineStr">
         <is>
-          <t>Maybe she figured that out from our earlier banter, or
-maybe her saying it doesn't hurt is a lie.</t>
+          <t>Maybe she figured that out from our earlier banter,
+or maybe her saying it doesn't hurt is a lie.</t>
         </is>
       </c>
       <c r="C1574" t="n">
@@ -24706,8 +24727,8 @@
       </c>
       <c r="B1582" s="1" t="inlineStr">
         <is>
-          <t>At the same time, I also felt resistance at the tip of
-my penis.</t>
+          <t>At the same time, I also felt resistance at the tip
+of my penis.</t>
         </is>
       </c>
       <c r="C1582" t="n">
@@ -25104,8 +25125,8 @@
       </c>
       <c r="B1608" s="1" t="inlineStr">
         <is>
-          <t>「...You know, people—beyond the lessons at Gakuen—also
-learn things in their own ways...」</t>
+          <t>「...You know, people—beyond the lessons at
+Gakuen—also learn things in their own ways...」</t>
         </is>
       </c>
       <c r="C1608" t="n">
@@ -25121,7 +25142,8 @@
       <c r="B1609" s="1" t="inlineStr">
         <is>
           <t>…I thought they were about to ask me how many dirty
-comics I read, so I said it wistfully to brush it off.</t>
+comics I read, so I said it wistfully to brush it
+off.</t>
         </is>
       </c>
       <c r="C1609" t="n">
@@ -25317,8 +25339,8 @@
       </c>
       <c r="B1622" s="1" t="inlineStr">
         <is>
-          <t>When I make them call me by my name, they suddenly get
-embarrassed.</t>
+          <t>When I make them call me by my name, they suddenly
+get embarrassed.</t>
         </is>
       </c>
       <c r="C1622" t="n">
@@ -25333,8 +25355,8 @@
       </c>
       <c r="B1623" s="1" t="inlineStr">
         <is>
-          <t>You're cuter when you go with your feelings instead of
-overthinking it...</t>
+          <t>You're cuter when you go with your feelings instead
+of overthinking it...</t>
         </is>
       </c>
       <c r="C1623" t="n">
@@ -25454,8 +25476,8 @@
       </c>
       <c r="B1631" s="1" t="inlineStr">
         <is>
-          <t>「Can you still not imagine what happens after I put my
-penis in？」</t>
+          <t>「Can you still not imagine what happens after I put
+my penis in？」</t>
         </is>
       </c>
       <c r="C1631" t="n">
@@ -25863,7 +25885,8 @@
       </c>
       <c r="B1658" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, that's right. This feels so good like this...！」</t>
+          <t>「Yeah, that's right. This feels so good like
+this...！」</t>
         </is>
       </c>
       <c r="C1658" t="n">
@@ -25970,8 +25993,8 @@
       </c>
       <c r="B1665" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nngh！ Uah... ah, ah...！ Hah... nngh！ Fnu, nngh,
-n~...！」</t>
+          <t>「Nn... nngh！ Uah... ah, ah...！ Hah... nngh！ Fnu,
+nngh, n~...！」</t>
         </is>
       </c>
       <c r="C1665" t="n">
@@ -26033,7 +26056,8 @@
       <c r="B1669" s="1" t="inlineStr">
         <is>
           <t>Each time I thrust my hips back and forth, zuryu...
-zuryutto, my penis is rubbed against the vaginal wall.</t>
+zuryutto, my penis is rubbed against the vaginal
+wall.</t>
         </is>
       </c>
       <c r="C1669" t="n">
@@ -26095,8 +26119,8 @@
       </c>
       <c r="B1673" s="1" t="inlineStr">
         <is>
-          <t>It really did seem to work, and Nono-chan's expression
-gradually eased as her discomfort faded.</t>
+          <t>It really did seem to work, and Nono-chan's
+expression gradually eased as her discomfort faded.</t>
         </is>
       </c>
       <c r="C1673" t="n">
@@ -26111,8 +26135,8 @@
       </c>
       <c r="B1674" s="1" t="inlineStr">
         <is>
-          <t>I didn't know whether to call it impressive or what to
-say….</t>
+          <t>I didn't know whether to call it impressive or what
+to say….</t>
         </is>
       </c>
       <c r="C1674" t="n">
@@ -26127,8 +26151,8 @@
       </c>
       <c r="B1675" s="1" t="inlineStr">
         <is>
-          <t>I couldn't help but force a wry smile in my heart, but
-thanks to that I felt a lot more at ease too.</t>
+          <t>I couldn't help but force a wry smile in my heart,
+but thanks to that I felt a lot more at ease too.</t>
         </is>
       </c>
       <c r="C1675" t="n">
@@ -26158,7 +26182,8 @@
       </c>
       <c r="B1677" s="1" t="inlineStr">
         <is>
-          <t>「Nono-chan. I want to keep moving, but… are you okay？」</t>
+          <t>「Nono-chan. I want to keep moving, but… are you
+okay？」</t>
         </is>
       </c>
       <c r="C1677" t="n">
@@ -26679,8 +26704,9 @@
       </c>
       <c r="B1711" s="1" t="inlineStr">
         <is>
-          <t>「Ah, no... I mean, how should I put it... my stomach's
-all restless, and I just can't stop that feeling...」</t>
+          <t>「Ah, no... I mean, how should I put it... my
+stomach's all restless, and I just can't stop that
+feeling...」</t>
         </is>
       </c>
       <c r="C1711" t="n">
@@ -27167,8 +27193,8 @@
       </c>
       <c r="B1743" s="1" t="inlineStr">
         <is>
-          <t>...With Nono-chan's choking breath, her belly draws in
-tight.</t>
+          <t>...With Nono-chan's choking breath, her belly draws
+in tight.</t>
         </is>
       </c>
       <c r="C1743" t="n">
@@ -27336,7 +27362,8 @@
       </c>
       <c r="B1754" s="1" t="inlineStr">
         <is>
-          <t>「Fueee! Hah, hahhh... ah! Ah! Ah! Hajime...! nghk...？」</t>
+          <t>「Fueee! Hah, hahhh... ah! Ah! Ah! Hajime...!
+nghk...？」</t>
         </is>
       </c>
       <c r="C1754" t="n">
@@ -28036,8 +28063,8 @@
       </c>
       <c r="B1800" s="1" t="inlineStr">
         <is>
-          <t>I walked them as far as the ferry deck to see them off
-and exchanged greetings with everyone.</t>
+          <t>I walked them as far as the ferry deck to see them
+off and exchanged greetings with everyone.</t>
         </is>
       </c>
       <c r="C1800" t="n">
@@ -28265,8 +28292,8 @@
       </c>
       <c r="B1815" s="1" t="inlineStr">
         <is>
-          <t>It's not class right now, but she seemed eager to play
-teacher during group activities like this.</t>
+          <t>It's not class right now, but she seemed eager to
+play teacher during group activities like this.</t>
         </is>
       </c>
       <c r="C1815" t="n">
@@ -28326,8 +28353,8 @@
       </c>
       <c r="B1819" s="1" t="inlineStr">
         <is>
-          <t>「Oh... Oji-sama, please make sure you brush your teeth
-every day, and also—...！ Ahhh！」</t>
+          <t>「Oh... Oji-sama, please make sure you brush your
+teeth every day, and also—...！ Ahhh！」</t>
         </is>
       </c>
       <c r="C1819" t="n">
@@ -28433,8 +28460,8 @@
       </c>
       <c r="B1826" s="1" t="inlineStr">
         <is>
-          <t>As everyone bustled aboard the ship and I watched them
-go, Nono-chan intertwined her pinky with mine.</t>
+          <t>As everyone bustled aboard the ship and I watched
+them go, Nono-chan intertwined her pinky with mine.</t>
         </is>
       </c>
       <c r="C1826" t="n">
@@ -28540,8 +28567,8 @@
       </c>
       <c r="B1833" s="1" t="inlineStr">
         <is>
-          <t>I could still see everyone's backs, so maybe I took it
-off thinking someone might turn around？</t>
+          <t>I could still see everyone's backs, so maybe I took
+it off thinking someone might turn around？</t>
         </is>
       </c>
       <c r="C1833" t="n">
@@ -28631,8 +28658,8 @@
       </c>
       <c r="B1839" s="1" t="inlineStr">
         <is>
-          <t>「Ah... yes, I was thinking of going home too, but it's
-really far... ehehe」</t>
+          <t>「Ah... yes, I was thinking of going home too, but
+it's really far... ehehe」</t>
         </is>
       </c>
       <c r="C1839" t="n">

--- a/processed_ruby_restored_xlsx/sc112_ノノ２：恋人化.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc112_ノノ２：恋人化.ss.xlsx
@@ -701,7 +701,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>「Ah, ah, Miru's going too！」</t>
+          <t>Ah, ah, Miru's going too！</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>「Then Rin will go...！」</t>
+          <t>Then Rin will go...！</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -838,7 +838,7 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>「Good work today, Nono-chan-sensei.」</t>
+          <t>Good work today, Nono-chan-sensei.</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1039,8 +1039,8 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, I guess so... what do you want to do over
-summer break？」</t>
+          <t>Yeah, I guess so... what do you want to do over
+summer break？</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha, you're pretty sloppy…！」</t>
+          <t>Ahaha, you」re pretty sloppy…！</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1132,9 +1132,9 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>「When you put it that way, yeah... it's just that I
+          <t>When you put it that way, yeah... it's just that I
 still don't know what I should do, so I think
-anything will be fun！」</t>
+anything will be fun！</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>「Eeeeeeeehhh？!」</t>
+          <t>Eeeeeeeehhh？!</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2898,7 +2898,7 @@
       <c r="B159" s="1" t="inlineStr">
         <is>
           <t>「Oh, Oji-sama is going to be the teacher？ I'm looking
-forward to what kind of lesson I'll give！」</t>
+forward to what kind of lesson he'll give！」</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -5725,8 +5725,9 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t>Because I'm usually in the teacher's position, I
-probably think making a ruckus during class is wrong.</t>
+          <t>Because he's usually in the teacher's position, he
+probably thinks making a ruckus during class is
+wrong.</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -9166,7 +9167,7 @@
       </c>
       <c r="B567" s="1" t="inlineStr">
         <is>
-          <t>「Mm… yes」</t>
+          <t>Mm… yes</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -14960,7 +14961,7 @@
       </c>
       <c r="B944" s="1" t="inlineStr">
         <is>
-          <t>「Wait, sorry！」</t>
+          <t>Wait, sorry！</t>
         </is>
       </c>
       <c r="C944" t="n">
@@ -15559,8 +15560,8 @@
       </c>
       <c r="B983" s="1" t="inlineStr">
         <is>
-          <t>「I want you to make it so she can stay at this
-academy even after summer break is over！」</t>
+          <t>「I want you to make it so she can stay at this gakuen
+even after summer break is over！」</t>
         </is>
       </c>
       <c r="C983" t="n">
@@ -15742,8 +15743,8 @@
       </c>
       <c r="B995" s="1" t="inlineStr">
         <is>
-          <t>Hearing her say it so nonchalantly, I couldn't help
-raising my voice.</t>
+          <t>Hearing her say it so nonchalantly, he couldn't help
+raising his voice.</t>
         </is>
       </c>
       <c r="C995" t="n">
@@ -15849,7 +15850,7 @@
       <c r="B1002" s="1" t="inlineStr">
         <is>
           <t>Her voice, stripped of inflection, snapped out the
-words, leaving me momentarily speechless.</t>
+words, leaving him momentarily speechless.</t>
         </is>
       </c>
       <c r="C1002" t="n">
@@ -15987,7 +15988,7 @@
       </c>
       <c r="B1011" s="1" t="inlineStr">
         <is>
-          <t>She dismissed it curtly with a rejection, and I
+          <t>She dismissed it curtly with a rejection, and he
 reflexively tried to press the point.</t>
         </is>
       </c>
@@ -17750,7 +17751,7 @@
       <c r="B1126" s="1" t="inlineStr">
         <is>
           <t>「Yes... Janitor-sensei suddenly went out, so I got
-worried and secretly followed me...」</t>
+worried and secretly followed him...」</t>
         </is>
       </c>
       <c r="C1126" t="n">
@@ -18254,8 +18255,8 @@
       </c>
       <c r="B1159" s="1" t="inlineStr">
         <is>
-          <t>Those feelings grew too strong, and I ended up making
-a move on Nono-chan.</t>
+          <t>Those feelings grew too strong, and he ended up
+making a move on Nono-chan.</t>
         </is>
       </c>
       <c r="C1159" t="n">
@@ -19203,8 +19204,8 @@
       </c>
       <c r="B1221" s="1" t="inlineStr">
         <is>
-          <t>「If possible, I'd like Nono-chan to stay on as a
-teacher at the Academy.」</t>
+          <t>If possible, I'd like Nono-chan to stay on as a
+teacher at the Academy.</t>
         </is>
       </c>
       <c r="C1221" t="n">
@@ -19796,7 +19797,7 @@
       </c>
       <c r="B1260" s="1" t="inlineStr">
         <is>
-          <t>Maybe she felt a little better thinking she was in
+          <t>Maybe they felt a little better thinking they were in
 the same position as me, who’s older.</t>
         </is>
       </c>
@@ -20345,7 +20346,7 @@
       </c>
       <c r="B1296" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nnn~...」</t>
+          <t>Nn... nnn~...</t>
         </is>
       </c>
       <c r="C1296" t="n">
@@ -20437,7 +20438,7 @@
       </c>
       <c r="B1302" s="1" t="inlineStr">
         <is>
-          <t>「Mmm! Nnngh... Ah...! Smooch! Smoooch!」</t>
+          <t>Mmm! Nnngh... Ah...! Smooch! Smoooch!</t>
         </is>
       </c>
       <c r="C1302" t="n">
@@ -21003,8 +21004,8 @@
       </c>
       <c r="B1339" s="1" t="inlineStr">
         <is>
-          <t>Suppressing the pounding in my chest as I asked,
-Nono-chan pressed her forehead to mine.</t>
+          <t>Suppressing the pounding in his chest as he asked,
+Nono-chan pressed her forehead to his.</t>
         </is>
       </c>
       <c r="C1339" t="n">
@@ -22261,8 +22262,8 @@
       </c>
       <c r="B1421" s="1" t="inlineStr">
         <is>
-          <t>With my fingertips I pinched and tugged a little, and
-the little nub puffed up.</t>
+          <t>With his fingertips he pinched and tugged a little,
+and the little nub puffed up.</t>
         </is>
       </c>
       <c r="C1421" t="n">
@@ -22399,8 +22400,8 @@
       </c>
       <c r="B1430" s="1" t="inlineStr">
         <is>
-          <t>When I gently rubbed the puckered nub, Nono-chan lost
-her words and shook her head.</t>
+          <t>When he gently rubbed the puckered nub, Nono-chan
+lost her words and shook her head.</t>
         </is>
       </c>
       <c r="C1430" t="n">
@@ -22524,7 +22525,7 @@
       </c>
       <c r="B1438" s="1" t="inlineStr">
         <is>
-          <t>「Heh heh...！ Yeah, I'm feeling it, you know？」</t>
+          <t>Heh heh...！ Yeah, I'm feeling it, you know？</t>
         </is>
       </c>
       <c r="C1438" t="n">
@@ -23819,8 +23820,8 @@
       </c>
       <c r="B1523" s="1" t="inlineStr">
         <is>
-          <t>I asked, steeling myself; after hesitating, Nono-chan
-desperately answered.</t>
+          <t>He asked, steeling himself; after hesitating,
+Nono-chan desperately answered.</t>
         </is>
       </c>
       <c r="C1523" t="n">
@@ -24037,7 +24038,7 @@
       </c>
       <c r="B1537" s="1" t="inlineStr">
         <is>
-          <t>「Say it properly all the way through, okay？」</t>
+          <t>Say it properly all the way through, okay？</t>
         </is>
       </c>
       <c r="C1537" t="n">
@@ -24297,7 +24298,7 @@
       </c>
       <c r="B1554" s="1" t="inlineStr">
         <is>
-          <t>「Nngh... nnk, fuh... nnh...！」</t>
+          <t>Nngh... nnk, fuh... nnh...！</t>
         </is>
       </c>
       <c r="C1554" t="n">
@@ -24697,7 +24698,7 @@
       </c>
       <c r="B1580" s="1" t="inlineStr">
         <is>
-          <t>「Nngh...！？　Nnkuh...！」</t>
+          <t>Nngh...！？　Nnkuh...！</t>
         </is>
       </c>
       <c r="C1580" t="n">
@@ -25050,7 +25051,7 @@
       </c>
       <c r="B1603" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, it's my first time. But I know, okay？」</t>
+          <t>Yeah, it's my first time. But I know, okay？</t>
         </is>
       </c>
       <c r="C1603" t="n">
@@ -25583,7 +25584,7 @@
       </c>
       <c r="B1638" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... so that's how it is—！」</t>
+          <t>Yeah... so that's how it is—！</t>
         </is>
       </c>
       <c r="C1638" t="n">
@@ -25688,7 +25689,7 @@
       </c>
       <c r="B1645" s="1" t="inlineStr">
         <is>
-          <t>「Mm... I-I'm okay...！」</t>
+          <t>Mm... I-I'm okay...！</t>
         </is>
       </c>
       <c r="C1645" t="n">
@@ -26055,9 +26056,9 @@
       </c>
       <c r="B1669" s="1" t="inlineStr">
         <is>
-          <t>Each time I thrust my hips back and forth, zuryu...
-zuryutto, my penis is rubbed against the vaginal
-wall.</t>
+          <t>Each time he thrusts his hips back and forth,
+zuryu... zuryutto, his penis is rubbed against the
+vaginal wall.</t>
         </is>
       </c>
       <c r="C1669" t="n">
@@ -26552,7 +26553,7 @@
       </c>
       <c r="B1701" s="1" t="inlineStr">
         <is>
-          <t>「I-I'm okay... I'm okay, but...」</t>
+          <t>I-I'm okay... I'm okay, but...</t>
         </is>
       </c>
       <c r="C1701" t="n">
@@ -26597,8 +26598,8 @@
       </c>
       <c r="B1704" s="1" t="inlineStr">
         <is>
-          <t>「I guess, since it's my first time, it might be a
-little painful？」</t>
+          <t>I guess, since it」s my first time, it might be a
+little painful？</t>
         </is>
       </c>
       <c r="C1704" t="n">
@@ -26643,7 +26644,7 @@
       </c>
       <c r="B1707" s="1" t="inlineStr">
         <is>
-          <t>When I eased the motion of my hips, Nono-chan said
+          <t>When he eased the motion of his hips, Nono-chan said
 that in a fluster.</t>
         </is>
       </c>
@@ -26812,8 +26813,8 @@
       </c>
       <c r="B1718" s="1" t="inlineStr">
         <is>
-          <t>「Nn! Nn-ah! Ah... ah, aaah! Ugh, uuh...! Huh, huh,
-huuh... un!」</t>
+          <t>Nn! Nn-ah! Ah... ah, aaah! Ugh, uuh...! Huh, huh,
+huuh... un!</t>
         </is>
       </c>
       <c r="C1718" t="n">
